--- a/fill-smoke.xlsx
+++ b/fill-smoke.xlsx
@@ -1,40 +1,89 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1\Desktop\excel-ai-addin-rc6\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB652ED-6330-477B-8229-BC5ADC8FE933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Данные" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q1 2026" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Данные" sheetId="1" r:id="rId1"/>
+    <sheet name="Q1" sheetId="2" r:id="rId2"/>
+    <sheet name="Q2" sheetId="3" r:id="rId3"/>
+    <sheet name="Q1 2026" sheetId="4" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="8">
+  <si>
+    <t>Товар</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>Товар 1</t>
+  </si>
+  <si>
+    <t>Товар 2</t>
+  </si>
+  <si>
+    <t>Товар 3</t>
+  </si>
+  <si>
+    <t>Товар 4</t>
+  </si>
+  <si>
+    <t>Товар 5</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -52,94 +101,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Sales" displayName="Sales" ref="A1:C6" headerRowCount="1">
-  <autoFilter ref="A1:C6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Sales" displayName="Sales" ref="A1:C6">
+  <autoFilter ref="A1:C6" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="Товар"/>
-    <tableColumn id="2" name="Q1"/>
-    <tableColumn id="3" name="Q2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Товар"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Q1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Q2"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -426,142 +417,225 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="555" row="2">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{A0EF2F64-C0FF-483D-9E68-D0D6FA2925C0}">
+  <we:reference id="5f2c9a41-1f7c-4f2b-9a0e-9c1f2d7b3e10" version="1.1.1.0" store="\\localhost\C$\Users\1\Desktop\excel-ai-addin-rc6\catalog" storeType="Filesystem"/>
+  <we:alternateReferences/>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Товар</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Товар 1</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>10</v>
-      </c>
-      <c r="C2" t="n">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Товар 2</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <f>'Q1'!A1</f>
+        <v>10</v>
+      </c>
+      <c r="F2">
+        <f>'Q1 2026'!A1</f>
+        <v>100</v>
+      </c>
+      <c r="G2">
+        <f>SUM(Sales[Q1])</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3">
         <v>20</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Товар 3</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+      <c r="E3">
+        <f>'Q1'!A1</f>
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <f>'Q1 2026'!A1</f>
+        <v>100</v>
+      </c>
+      <c r="G3">
+        <f>SUM(Sales[Q1])</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
         <v>30</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>3</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Товар 4</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+      <c r="E4">
+        <f>'Q1'!A1</f>
+        <v>10</v>
+      </c>
+      <c r="F4">
+        <f>'Q1 2026'!A1</f>
+        <v>100</v>
+      </c>
+      <c r="G4">
+        <f>SUM(Sales[Q1])</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
         <v>40</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>4</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Товар 5</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+      <c r="E5">
+        <f>'Q1'!A1</f>
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <f>'Q1 2026'!A1</f>
+        <v>100</v>
+      </c>
+      <c r="G5">
+        <f>SUM(Sales[Q1])</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6">
         <v>50</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>5</v>
+      </c>
+      <c r="E6">
+        <f>'Q1'!A1</f>
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <f>'Q1 2026'!A1</f>
+        <v>100</v>
+      </c>
+      <c r="G6">
+        <f>SUM(Sales[Q1])</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E8">
+        <f>'Q1'!A1</f>
+        <v>10</v>
+      </c>
+      <c r="F8">
+        <f>'Q1'!A1</f>
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <f>'Q1'!A1</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E10" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E11" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E12" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B1" t="n">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>10</v>
+      </c>
+      <c r="B1">
         <v>11</v>
       </c>
-      <c r="C1" t="n">
+      <c r="C1">
         <v>12</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>20</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>30</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>40</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>50</v>
       </c>
     </row>
@@ -571,36 +645,32 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="n">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1">
         <v>1</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>2</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>3</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>4</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>5</v>
       </c>
     </row>
@@ -610,36 +680,32 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="n">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1">
         <v>100</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>200</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>300</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>400</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>500</v>
       </c>
     </row>

--- a/fill-smoke.xlsx
+++ b/fill-smoke.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1\Desktop\excel-ai-addin-rc6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB652ED-6330-477B-8229-BC5ADC8FE933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07138EB1-1677-411C-B04C-0BC4D7C4783D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -419,7 +419,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="555" row="2">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="3">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -437,10 +437,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -451,7 +451,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -473,8 +473,20 @@
         <f>SUM(Sales[Q1])</f>
         <v>150</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I2">
+        <f>'Q1'!A1</f>
+        <v>10</v>
+      </c>
+      <c r="J2">
+        <f>'Q1 2026'!A1</f>
+        <v>100</v>
+      </c>
+      <c r="K2">
+        <f>'Q1'!A1</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -496,8 +508,16 @@
         <f>SUM(Sales[Q1])</f>
         <v>150</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I3">
+        <f>'Q1'!A2</f>
+        <v>20</v>
+      </c>
+      <c r="J3">
+        <f>'Q1 2026'!A2</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -519,8 +539,16 @@
         <f>SUM(Sales[Q1])</f>
         <v>150</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I4">
+        <f>'Q1'!A3</f>
+        <v>30</v>
+      </c>
+      <c r="J4">
+        <f>'Q1 2026'!A3</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -542,8 +570,16 @@
         <f>SUM(Sales[Q1])</f>
         <v>150</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I5">
+        <f>'Q1'!A4</f>
+        <v>40</v>
+      </c>
+      <c r="J5">
+        <f>'Q1 2026'!A4</f>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -565,8 +601,16 @@
         <f>SUM(Sales[Q1])</f>
         <v>150</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I6">
+        <f>'Q1'!A5</f>
+        <v>50</v>
+      </c>
+      <c r="J6">
+        <f>'Q1 2026'!A5</f>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E8">
         <f>'Q1'!A1</f>
         <v>10</v>
@@ -579,18 +623,30 @@
         <f>'Q1'!A1</f>
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I8">
+        <f>'Q1'!A1</f>
+        <v>10</v>
+      </c>
+      <c r="J8">
+        <f>'Q1'!B1</f>
+        <v>11</v>
+      </c>
+      <c r="K8">
+        <f>'Q1'!C1</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E10" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E11" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E12" s="2" t="s">
         <v>3</v>
       </c>
